--- a/Test_Data/Opencart_Login_Data.xlsx
+++ b/Test_Data/Opencart_Login_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39e57f69de943d70/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Manual testing\Automation Project\Test_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEAEFF22-B97B-4C81-9344-82C8922D1642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B797E23-547B-4FC0-8D41-A0552335EF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{33F78B2B-0BC8-4B2E-ACC1-2E97C81B5D1A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Username</t>
   </si>
@@ -65,6 +65,9 @@
   <si>
     <t xml:space="preserve">Admin@gmail.com
 </t>
+  </si>
+  <si>
+    <t>Admin@121</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
